--- a/Result/18-12-24/HKEXstock_18-12-24period60RS80.xlsx
+++ b/Result/18-12-24/HKEXstock_18-12-24period60RS80.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/18-12-24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6691DDE6-F160-3B48-98EC-835EC460D7C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5891C75-7F6C-3940-B14E-4490C70E3F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -929,7 +929,7 @@
       </c>
     </row>
     <row r="3" spans="1:41">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>45</v>
       </c>
       <c r="B3">
